--- a/注塑项目/金榕/lucid汽车地板舱盖配件/地板舱盖- 新模预排计划7-5.xlsx
+++ b/注塑项目/金榕/lucid汽车地板舱盖配件/地板舱盖- 新模预排计划7-5.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chensiyuan5/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chensiyuan5/Desktop/Github/shenyuan_work/注塑项目/金榕/lucid汽车地板舱盖配件/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11D43A5-6AC1-5142-9336-50261C8454DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9725D013-55FA-F548-805C-B8258E3117DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9400" yWindow="2400" windowWidth="27940" windowHeight="12380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -401,6 +401,9 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -432,9 +435,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1259,9 +1259,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>3429000</xdr:colOff>
+      <xdr:colOff>2661755</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>1011916</xdr:rowOff>
+      <xdr:rowOff>444500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1285,7 +1285,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="673100" y="3670300"/>
-          <a:ext cx="3429000" cy="2535916"/>
+          <a:ext cx="2661755" cy="1968500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1294,6 +1294,50 @@
         <a:ln w="9525">
           <a:noFill/>
         </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2959100</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>4309269</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>876300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C6AB32B-6550-6476-9477-2CA79C78F71B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3632200" y="3670300"/>
+          <a:ext cx="1350169" cy="2400300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -1565,38 +1609,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="30" customHeight="1">
-      <c r="A1" s="19"/>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="20"/>
+      <c r="A1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+      <c r="P1" s="21"/>
+      <c r="Q1" s="21"/>
+      <c r="R1" s="21"/>
+      <c r="S1" s="21"/>
+      <c r="T1" s="21"/>
+      <c r="U1" s="21"/>
+      <c r="V1" s="21"/>
+      <c r="W1" s="21"/>
+      <c r="X1" s="21"/>
+      <c r="Y1" s="21"/>
     </row>
     <row r="2" spans="1:25" ht="30" customHeight="1">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="26"/>
       <c r="D2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1659,9 +1703,9 @@
       </c>
     </row>
     <row r="3" spans="1:25" ht="30" customHeight="1">
-      <c r="A3" s="21"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="25"/>
+      <c r="A3" s="22"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="26"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5" t="s">
         <v>20</v>
@@ -1722,9 +1766,9 @@
       </c>
     </row>
     <row r="4" spans="1:25" ht="100" customHeight="1">
-      <c r="A4" s="21"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="25"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="26"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
@@ -1749,9 +1793,9 @@
       <c r="Y4" s="17"/>
     </row>
     <row r="5" spans="1:25" ht="30" customHeight="1">
-      <c r="A5" s="21"/>
-      <c r="B5" s="24"/>
-      <c r="C5" s="25"/>
+      <c r="A5" s="22"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="26"/>
       <c r="D5" s="5" t="s">
         <v>21</v>
       </c>
@@ -1810,9 +1854,9 @@
       <c r="Y5" s="17"/>
     </row>
     <row r="6" spans="1:25" ht="30" customHeight="1">
-      <c r="A6" s="22"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="27"/>
+      <c r="A6" s="23"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="28"/>
       <c r="D6" s="5" t="s">
         <v>22</v>
       </c>
@@ -1873,11 +1917,11 @@
       </c>
     </row>
     <row r="7" spans="1:25" ht="30" customHeight="1">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="29"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="30"/>
       <c r="D7" s="11" t="s">
         <v>1</v>
       </c>
@@ -1946,9 +1990,9 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="30" customHeight="1">
-      <c r="A8" s="21"/>
-      <c r="B8" s="24"/>
-      <c r="C8" s="25"/>
+      <c r="A8" s="22"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="26"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5" t="s">
@@ -2001,9 +2045,9 @@
       <c r="Y8" s="17"/>
     </row>
     <row r="9" spans="1:25" ht="100" customHeight="1">
-      <c r="A9" s="21"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="25"/>
+      <c r="A9" s="22"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="26"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
@@ -2028,9 +2072,9 @@
       <c r="Y9" s="17"/>
     </row>
     <row r="10" spans="1:25" ht="30" customHeight="1">
-      <c r="A10" s="21"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="25"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="26"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5" t="s">
@@ -2075,9 +2119,9 @@
       <c r="Y10" s="17"/>
     </row>
     <row r="11" spans="1:25" ht="30" customHeight="1">
-      <c r="A11" s="22"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="27"/>
+      <c r="A11" s="23"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="28"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5" t="s">
@@ -2157,110 +2201,110 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="30">
+      <c r="A2" s="19">
         <v>1</v>
       </c>
-      <c r="B2" s="30"/>
+      <c r="B2" s="19"/>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="30"/>
-      <c r="B3" s="30"/>
+      <c r="A3" s="19"/>
+      <c r="B3" s="19"/>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="30"/>
-      <c r="B4" s="30"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="30"/>
-      <c r="B5" s="30"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="30"/>
-      <c r="B6" s="30"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="30"/>
-      <c r="B7" s="30"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="30"/>
-      <c r="B8" s="30"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
     </row>
     <row r="9" spans="1:2" ht="141" customHeight="1">
-      <c r="A9" s="30"/>
-      <c r="B9" s="30"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="30">
+      <c r="A10" s="19">
         <v>2</v>
       </c>
-      <c r="B10" s="30"/>
+      <c r="B10" s="19"/>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="30"/>
-      <c r="B11" s="30"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="30"/>
-      <c r="B12" s="30"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="30"/>
-      <c r="B13" s="30"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="30"/>
-      <c r="B14" s="30"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="30"/>
-      <c r="B15" s="30"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="30"/>
-      <c r="B16" s="30"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="30"/>
-      <c r="B17" s="30"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
     </row>
     <row r="18" spans="1:2" ht="102" customHeight="1">
-      <c r="A18" s="30"/>
-      <c r="B18" s="30"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="30">
+      <c r="A19" s="19">
         <v>3</v>
       </c>
-      <c r="B19" s="30"/>
+      <c r="B19" s="19"/>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="30"/>
-      <c r="B20" s="30"/>
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="30"/>
-      <c r="B21" s="30"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="30"/>
-      <c r="B22" s="30"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="30"/>
-      <c r="B23" s="30"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="30"/>
-      <c r="B24" s="30"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="30"/>
-      <c r="B25" s="30"/>
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
     </row>
     <row r="26" spans="1:2" ht="101" customHeight="1">
-      <c r="A26" s="30"/>
-      <c r="B26" s="30"/>
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="6">
